--- a/PMI-DZT2/ПМИ ТокЗ/pmi_tokzdzt/rtponn_modes/РТПО_5.xlsx
+++ b/PMI-DZT2/ПМИ ТокЗ/pmi_tokzdzt/rtponn_modes/РТПО_5.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SGF_Parameters" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,14 +12,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outputs" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,21 +28,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF0000"/>
-        <bgColor rgb="00FF0000"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -55,10 +57,19 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -69,10 +80,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -441,82 +454,82 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_hvptoc1_tovctoc</t>
+          <t>TOVCTOC_1_HVPTOC1_EnaDis</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_ptoc1_tovctoc</t>
+          <t>TOVCTOC_1_PTOC1_EnaDis</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_ptoc2_tovctoc</t>
+          <t>TOVCTOC_1_PTOC2_EnaDis</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_ptoc1_lvarctoc</t>
+          <t>LVARCTOC_1_PTOC1_EnaDis</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_ptoc1_ltcblktoc</t>
+          <t>LTCBLKTOC_1_PTOC1_EnaDis</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_hvptoc1_strtpalc</t>
+          <t>STRTPALC_1_HVPTOC1_EnaDis</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_lvptoc1_strtpalc</t>
+          <t>STRTPALC_1_LVPTOC1_EnaDis</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_lvptoc2_strtpalc</t>
+          <t>STRTPALC_1_LVPTOC2_EnaDis</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_hvptoc1_tpalc</t>
+          <t>TPALC_1_HVPTOC1_EnaDis</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_lvptoc1_tpalc</t>
+          <t>TPALC_1_LVPTOC1_EnaDis</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_lvptoc2_tpalc</t>
+          <t>TPALC_1_LVPTOC2_EnaDis</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_palc1_eqpalc</t>
+          <t>EQPALC_1_PALC1_EnaDis</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>SGF2_palc1_eqpalc</t>
+          <t>EQPALC_1_PALC1_CurrCtrlEna</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>SGF3_palc1_eqpalc</t>
+          <t>EQPALC_1_PALC1_OilTmpCtrlEna</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_ptrc1_tprmofflvlgc</t>
+          <t>TPRMOFFLVLGC_1_PTRC1_EnaDis</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_rbre1_tprmofflvlgc</t>
+          <t>TPRMOFFLVLGC_1_RBRE1_EnaDis</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
@@ -611,77 +624,77 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>T1_hvptoc1_tovctoc</t>
+          <t>TOVCTOC_1_HVPTOC1_Top</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Iset_hvptoc1_tovctoc</t>
+          <t>TOVCTOC_1_HVPTOC1_Iop</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>T1_ptoc1_tovctoc</t>
+          <t>TOVCTOC_1_PTOC1_Top</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Iset_ptoc1_tovctoc</t>
+          <t>TOVCTOC_1_PTOC1_Iop</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>T1_ptoc2_tovctoc</t>
+          <t>TOVCTOC_1_PTOC2_Top</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Iset_ptoc2_tovctoc</t>
+          <t>TOVCTOC_1_PTOC2_Iop</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Iset_ptoc1_lvarctoc</t>
+          <t>LVARCTOC_1_PTOC1_Iop</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Iset_ptoc1_ltcblktoc</t>
+          <t>LTCBLKTOC_1_PTOC1_Iop</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Iset_hvptoc1_strtpalc</t>
+          <t>STRTPALC_1_HVPTOC1_Iop</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Iset_lvptoc1_strtpalc</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Iset_lvptoc2_strtpalc</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Iset_hvptoc1_tpalc</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Iset_lvptoc1_tpalc</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Iset_lvptoc2_tpalc</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>T1_palc1_eqpalc</t>
+          <t>STRTPALC_1_LVPTOC1_Iop</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>STRTPALC_1_LVPTOC2_Iop</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>TPALC_1_HVPTOC1_Iop</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>TPALC_1_LVPTOC1_Iop</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>TPALC_1_LVPTOC2_Iop</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>EQPALC_1_PALC1_Top</t>
         </is>
       </c>
     </row>
@@ -743,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -777,129 +790,119 @@
           <t>IC1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>VYVOD</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>OV_tovctoc</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>OV_hvptoc1_tovctoc</t>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>DI_ControllerDisable</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>DI_TOVCTOC</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>DI_TOVCTOC_HVPTOC1</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>NaOtkl_tovctoc</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>OV_ptoc1_tovctoc</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>NaOtkl_ptoc1_tovctoc</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>OV_ptoc2_tovctoc</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>NaOtkl_ptoc2_tovctoc</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>OV_ptoc1_lvarctoc</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>OV_ptoc1_ltcblktoc</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>OV_strpalc</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
+          <t>DI_TOVCTOC_Sign</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>DI_TOVCTOC_LVPTOC1</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>DI_TOVCTOC_LVPTOC2</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>DI_LVARCTOC</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>DI_LTCBLKTOC</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>DI_STRTPALC</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>OV_hvptoc1_strpalc</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>OV_lvptoc1_strpalc</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>OV_lvptoc2_strpalc</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>OV_tpalc</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>OV_hvptoc1_tpalc</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>OV_lvptoc1_tpalc</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>OV_lvptoc2_tpalc</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>OV_eqpalc</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>NaSign_eqpalc</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>otkaz_so</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>t_masla_zpo</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>OV_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>OV_ptrc1_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>OV_rbre1_tprmofflvlgc</t>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>DI_STRTPALC_LVPTOC1</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>DI_STRTPALC_LVPTOC2</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>DI_TPALC</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>DI_TPALC_HVPTOC1</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>DI_TPALC_LVPTOC1</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>DI_TPALC_LVPTOC2</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>DI_EQPALC</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t>DI_EQPALC_Sign</t>
+        </is>
+      </c>
+      <c r="Y1" s="2" t="inlineStr">
+        <is>
+          <t>FailCoolSys</t>
+        </is>
+      </c>
+      <c r="Z1" s="2" t="inlineStr">
+        <is>
+          <t>AlcOilTmp</t>
+        </is>
+      </c>
+      <c r="AA1" s="2" t="inlineStr">
+        <is>
+          <t>DI_TPRMOFFLVLGC</t>
+        </is>
+      </c>
+      <c r="AB1" s="2" t="inlineStr">
+        <is>
+          <t>DI_TJNTPTRC</t>
+        </is>
+      </c>
+      <c r="AC1" s="2" t="inlineStr">
+        <is>
+          <t>DI_JNTRBRE</t>
         </is>
       </c>
     </row>
@@ -989,12 +992,6 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1013,314 +1010,314 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_hvptoc1_tovctoc</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_hvptoc1_tovctoc</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>pusk_hvptoc1_tovctoc</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>io_hvptoc1_tovctoc</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>srab_hvptoc1_tovctoc</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>srabotkl_hvptoc1_tovctoc</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_ptoc1_tovctoc</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_ptoc1_tovctoc</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>pusk_ptoc1_tovctoc</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>io_ptoc1_tovctoc</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>srab_ptoc1_tovctoc</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>srabotkl_ptoc1_tovctoc</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_ptoc2_tovctoc</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_ptoc2_tovctoc</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>pusk_ptoc2_tovctoc</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>io_ptoc2_tovctoc</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>srab_ptoc2_tovctoc</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>srabotkl_ptoc2_tovctoc</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>srab_tovctoc</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_ptoc1_lvarctoc</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_ptoc1_lvarctoc</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>pusk_ptoc1_lvarctoc</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>io_ptoc1_lvarctoc</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_ptoc1_ltcblktoc</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_ptoc1_ltcblktoc</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>pusk_ptoc1_ltcblktoc</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>io_ptoc1_ltcblktoc</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_hvptoc1_strpalc</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_hvptoc1_strpalc</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>pusk_hvptoc1_strpalc</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>io_hvptoc1_strpalc</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_lvptoc1_strpalc</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_lvptoc1_strpalc</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>pusk_lvptoc1_strpalc</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>io_lvptoc1_strpalc</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_lvptoc2_strpalc</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_lvptoc2_strpalc</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>pusk_lvptoc2_strpalc</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>io_lvptoc2_strpalc</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>pusk_strpalc</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_strpalc</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_hvptoc1_tpalc</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_hvptoc1_tpalc</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>pusk_hvptoc1_tpalc</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>io_hvptoc1_tpalc</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_lvptoc1_tpalc</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_lvptoc1_tpalc</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>pusk_lvptoc1_tpalc</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>io_lvptoc1_tpalc</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_lvptoc2_tpalc</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_lvptoc2_tpalc</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>pusk_lvptoc2_tpalc</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>io_lvptoc2_tpalc</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>pusk_tpalc</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_tpalc</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_lvoileqpalc_eqpalc</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_lvoileqpalc_eqpalc</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>pusk_lvoileqpalc_eqpalc</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>srabsign_lvoileqpalc_eqpalc</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>srab_lvoileqpalc_eqpalc</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_ptrc1_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_ptrc1_tprmofflvlgc</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>TOVCTOC_1_HVPTOC1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>TOVCTOC_1_HVPTOC1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>TOVCTOC_1_HVPTOC1_Str</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>TOVCTOC_1_HVPTOC1_DE_I</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>TOVCTOC_1_HVPTOC1_Op</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>TOVCTOC_1_HVPTOC1_OpOnTrip</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>TOVCTOC_1_PTOC1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>TOVCTOC_1_PTOC1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>TOVCTOC_1_PTOC1_Str</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>TOVCTOC_1_PTOC1_DE_I</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>TOVCTOC_1_PTOC1_Op</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>TOVCTOC_1_PTOC1_OpOnTrip</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>TOVCTOC_1_PTOC2_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>TOVCTOC_1_PTOC2_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>TOVCTOC_1_PTOC2_Str</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>TOVCTOC_1_PTOC2_DE_I</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>TOVCTOC_1_PTOC2_Op</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>TOVCTOC_1_PTOC2_OpOnTrip</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>TOVCTOC_1_TOVCTOC_Op</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>LVARCTOC_1_PTOC1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>LVARCTOC_1_PTOC1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>LVARCTOC_1_PTOC1_Str</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>LVARCTOC_1_PTOC1_DE_I</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t>LTCBLKTOC_1_PTOC1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="Y1" s="2" t="inlineStr">
+        <is>
+          <t>LTCBLKTOC_1_PTOC1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="Z1" s="2" t="inlineStr">
+        <is>
+          <t>LTCBLKTOC_1_PTOC1_Str</t>
+        </is>
+      </c>
+      <c r="AA1" s="2" t="inlineStr">
+        <is>
+          <t>LTCBLKTOC_1_PTOC1_DE_I</t>
+        </is>
+      </c>
+      <c r="AB1" s="2" t="inlineStr">
+        <is>
+          <t>STRTPALC_1_HVPTOC1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="AC1" s="2" t="inlineStr">
+        <is>
+          <t>STRTPALC_1_HVPTOC1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="AD1" s="2" t="inlineStr">
+        <is>
+          <t>STRTPALC_1_HVPTOC1_Str</t>
+        </is>
+      </c>
+      <c r="AE1" s="2" t="inlineStr">
+        <is>
+          <t>STRTPALC_1_HVPTOC1_DE_I</t>
+        </is>
+      </c>
+      <c r="AF1" s="2" t="inlineStr">
+        <is>
+          <t>STRTPALC_1_LVPTOC1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="AG1" s="2" t="inlineStr">
+        <is>
+          <t>STRTPALC_1_LVPTOC1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="AH1" s="2" t="inlineStr">
+        <is>
+          <t>STRTPALC_1_LVPTOC1_Str</t>
+        </is>
+      </c>
+      <c r="AI1" s="2" t="inlineStr">
+        <is>
+          <t>STRTPALC_1_LVPTOC1_DE_I</t>
+        </is>
+      </c>
+      <c r="AJ1" s="2" t="inlineStr">
+        <is>
+          <t>STRTPALC_1_LVPTOC2_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="AK1" s="2" t="inlineStr">
+        <is>
+          <t>STRTPALC_1_LVPTOC2_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="AL1" s="2" t="inlineStr">
+        <is>
+          <t>STRTPALC_1_LVPTOC2_Str</t>
+        </is>
+      </c>
+      <c r="AM1" s="2" t="inlineStr">
+        <is>
+          <t>STRTPALC_1_LVPTOC2_DE_I</t>
+        </is>
+      </c>
+      <c r="AN1" s="2" t="inlineStr">
+        <is>
+          <t>STRTPALC_1_PTOC1_Str</t>
+        </is>
+      </c>
+      <c r="AO1" s="2" t="inlineStr">
+        <is>
+          <t>STRTPALC_1_PTOC1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="AP1" s="2" t="inlineStr">
+        <is>
+          <t>TPALC_1_HVPTOC1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="AQ1" s="2" t="inlineStr">
+        <is>
+          <t>TPALC_1_HVPTOC1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="AR1" s="2" t="inlineStr">
+        <is>
+          <t>TPALC_1_HVPTOC1_Str</t>
+        </is>
+      </c>
+      <c r="AS1" s="2" t="inlineStr">
+        <is>
+          <t>TPALC_1_HVPTOC1_DE_I</t>
+        </is>
+      </c>
+      <c r="AT1" s="2" t="inlineStr">
+        <is>
+          <t>TPALC_1_LVPTOC1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="AU1" s="2" t="inlineStr">
+        <is>
+          <t>TPALC_1_LVPTOC1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="AV1" s="2" t="inlineStr">
+        <is>
+          <t>TPALC_1_LVPTOC1_Str</t>
+        </is>
+      </c>
+      <c r="AW1" s="2" t="inlineStr">
+        <is>
+          <t>TPALC_1_LVPTOC1_DE_I</t>
+        </is>
+      </c>
+      <c r="AX1" s="2" t="inlineStr">
+        <is>
+          <t>TPALC_1_LVPTOC2_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="AY1" s="2" t="inlineStr">
+        <is>
+          <t>TPALC_1_LVPTOC2_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="AZ1" s="2" t="inlineStr">
+        <is>
+          <t>TPALC_1_LVPTOC2_Str</t>
+        </is>
+      </c>
+      <c r="BA1" s="2" t="inlineStr">
+        <is>
+          <t>TPALC_1_LVPTOC2_DE_I</t>
+        </is>
+      </c>
+      <c r="BB1" s="2" t="inlineStr">
+        <is>
+          <t>TPALC_1_PTOC1_Str</t>
+        </is>
+      </c>
+      <c r="BC1" s="2" t="inlineStr">
+        <is>
+          <t>TPALC_1_PTOC1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="BD1" s="2" t="inlineStr">
+        <is>
+          <t>EQPALC_1_PALC1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="BE1" s="2" t="inlineStr">
+        <is>
+          <t>EQPALC_1_PALC1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="BF1" s="2" t="inlineStr">
+        <is>
+          <t>EQPALC_1_PALC1_Str</t>
+        </is>
+      </c>
+      <c r="BG1" s="2" t="inlineStr">
+        <is>
+          <t>EQPALC_1_PALC1_OpOnSignal</t>
+        </is>
+      </c>
+      <c r="BH1" s="2" t="inlineStr">
+        <is>
+          <t>EQPALC_1_PALC1_Op</t>
+        </is>
+      </c>
+      <c r="BI1" s="2" t="inlineStr">
+        <is>
+          <t>TPRMOFFLVLGC_1_PTRC1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="BJ1" s="2" t="inlineStr">
+        <is>
+          <t>TPRMOFFLVLGC_1_PTRC1_FuncOperDisabled</t>
         </is>
       </c>
       <c r="BK1" s="1" t="inlineStr">
@@ -1328,29 +1325,29 @@
           <t>pusk_ptrc1_tprmofflvlgc</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>srab_ptrc1_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_rbre1_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_rbre1_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>zapret_rbre1_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>pusk_lvalh</t>
+      <c r="BL1" s="2" t="inlineStr">
+        <is>
+          <t>TPRMOFFLVLGC_1_PTRC1_Op</t>
+        </is>
+      </c>
+      <c r="BM1" s="2" t="inlineStr">
+        <is>
+          <t>TPRMOFFLVLGC_1_RBRE1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="BN1" s="2" t="inlineStr">
+        <is>
+          <t>TPRMOFFLVLGC_1_RBRE1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="BO1" s="2" t="inlineStr">
+        <is>
+          <t>TPRMOFFLVLGC_1_RBRE1_BlkOp</t>
+        </is>
+      </c>
+      <c r="BP1" s="2" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_Alarm</t>
         </is>
       </c>
     </row>
